--- a/daily_matches/job_matches_2026-03-27.xlsx
+++ b/daily_matches/job_matches_2026-03-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data</t>
+          <t>Sr AI ML Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Docker, Kubernetes, Apache Airflow, CI/CD, Git, Databricks, Kafka, NoSQL</t>
+          <t>RAG, Prompt Engineering, TensorFlow, BigQuery, Docker, CI/CD, Databricks, BigQuery, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a76b23bc92692fef</t>
+          <t>https://www.indeed.com/viewjob?jk=c97a6763a721f8de</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Azure Deployment Engineer &amp; Coordinator</t>
+          <t>AI Software Engineer (Analytical Agents) Hybrid</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Azure ML, Docker, Kubernetes, AKS, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, BigQuery, Git, BigQuery, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66edde0eee044f22</t>
+          <t>https://www.indeed.com/viewjob?jk=49e09abe4097363d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Research &amp; Agentic Engineer Hybrid</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ease Logistics Services LLC</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dublin, OH, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, CI/CD, Terraform, Power BI, SQL, R, Scala</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Gemini, Copilot, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1174e0c00dce1a</t>
+          <t>https://www.indeed.com/viewjob?jk=823e3455042038c1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TEST ENGINEER</t>
+          <t>Machine Learning Engineer III</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Peraton</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Java</t>
+          <t>Machine Learning Engineer, TensorFlow, PyTorch, Docker, Kubernetes, Git, Databricks, Hadoop, Python, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,77 +601,357 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19ffd8579c25846e</t>
+          <t>https://www.indeed.com/viewjob?jk=a3b0859d9457f7e5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ground Data Software Engineer - Early Career</t>
+          <t>Relevance Engineer â€“ Enterprise Search &amp; AI Hybrid</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Littleton, CO, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Dataflow, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Git, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=686b463f732f1fc3</t>
+          <t>https://www.indeed.com/viewjob?jk=d3e302deecc02528</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>AI Architect Agentic &amp; Generative AI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TriWest Healthcare Alliance</t>
+          <t>Select Minds LLC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, S3, CI/CD, Python, R, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5060ec023c731cc5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>mLabs</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
         <v>10</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Tableau, Power BI, Python, SQL, R, Java, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, MongoDB, Cassandra, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd162baab07aee87</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>mLabs</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, MongoDB, Cassandra, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c4cb33b74b3d3a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior Specialty Software Engineer - Enterprise Generative AI Platform UI and Python Engineering</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e0ebbdc8280a898d</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior Specialty Software Engineer - Enterprise Generative AI Platform UI and Python Engineering</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Concord, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc98d4ed7a5637a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Specialty Software Engineer - Enterprise Generative AI Platform UI and Python Engineering</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b3a67d4cb4f58965</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AI Platform Security Engineer Hybrid</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Research Triangle Park, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Scala</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=00516809ddff245c</t>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c0ed7b5d7439d27c</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Milpitas, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cda2f2d7bf7fdef8</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>R&amp;D Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Yokogawa</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Santa Fe, NM, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Docker, Kubernetes, CI/CD, Git, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e6246aba8708cc71</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-27.xlsx
+++ b/daily_matches/job_matches_2026-03-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr AI ML Engineer</t>
+          <t>GCP AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, TensorFlow, BigQuery, Docker, CI/CD, Databricks, BigQuery, MySQL, MongoDB</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Gemini, TensorFlow, PyTorch, Data Lake, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c97a6763a721f8de</t>
+          <t>https://www.indeed.com/viewjob?jk=90a4bbd6dc8ae1d0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Software Engineer (Analytical Agents) Hybrid</t>
+          <t>AI/ML Engineer with AWS SageMaker</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, BigQuery, Git, BigQuery, Python</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Gemini, TensorFlow, PyTorch, XGBoost, AWS SageMaker, S3</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49e09abe4097363d</t>
+          <t>https://www.indeed.com/viewjob?jk=3717cba2b9262b6d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Research &amp; Agentic Engineer Hybrid</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Gemini, Copilot, Docker, Kubernetes, Git</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, TensorFlow, PyTorch, Redshift, Git, Snowflake, Redshift</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=823e3455042038c1</t>
+          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer III</t>
+          <t>Infrastructure DevOps Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Wellington, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, TensorFlow, PyTorch, Docker, Kubernetes, Git, Databricks, Hadoop, Python, R</t>
+          <t>RAG, Gemini, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b0859d9457f7e5</t>
+          <t>https://www.indeed.com/viewjob?jk=36619f835bea4f18</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Relevance Engineer â€“ Enterprise Search &amp; AI Hybrid</t>
+          <t>Java Python Full Stack Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Git, Python, R, Java, Scala, Optimization</t>
+          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3e302deecc02528</t>
+          <t>https://www.indeed.com/viewjob?jk=d1dd947a7f977e8c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Architect Agentic &amp; Generative AI</t>
+          <t>Infrastructure Engineer (Backend)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Select Minds LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, S3, CI/CD, Python, R, Optimization, A/B Testing</t>
+          <t>RAG, Glue, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5060ec023c731cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=9275dfa105600f9f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Infrastructure Engineer (Backend)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mLabs</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, MongoDB, Cassandra, Python, SQL, R, Scala</t>
+          <t>RAG, Glue, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd162baab07aee87</t>
+          <t>https://www.indeed.com/viewjob?jk=fbda2b1be4a20921</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Infrastructure Engineer (Backend)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mLabs</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, MongoDB, Cassandra, Python, SQL, R, Scala</t>
+          <t>RAG, Glue, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c4cb33b74b3d3a5</t>
+          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer - Enterprise Generative AI Platform UI and Python Engineering</t>
+          <t>Senior Data Engineer - APIs</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>RAG, BigQuery, Dataflow, Kubernetes, CI/CD, Git, BigQuery, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0ebbdc8280a898d</t>
+          <t>https://www.indeed.com/viewjob?jk=734740ee36ff607d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer - Enterprise Generative AI Platform UI and Python Engineering</t>
+          <t>Sr Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>AT&amp;T</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Keras, MLflow, Databricks, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc98d4ed7a5637a5</t>
+          <t>https://www.indeed.com/viewjob?jk=38426988b285acce</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer - Enterprise Generative AI Platform UI and Python Engineering</t>
+          <t>Software Engineer III (Java/SpringBoot/Kafka/Cloud)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>RAG, Copilot, Terraform, Git, Snowflake, Kafka, Cassandra, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3a67d4cb4f58965</t>
+          <t>https://www.indeed.com/viewjob?jk=e37f813b5cb175d0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Platform Security Engineer Hybrid</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Scala</t>
+          <t>Data Scientist, RAG, Redshift, Git, Snowflake, Redshift, MySQL, NoSQL, Tableau, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0ed7b5d7439d27c</t>
+          <t>https://www.indeed.com/viewjob?jk=9a2a8cc873c5ddd1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Consultant Analytical Engineer Expanse</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Scala, Optimization</t>
+          <t>RAG, Redshift, Redshift, Hadoop, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,42 +916,217 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cda2f2d7bf7fdef8</t>
+          <t>https://www.indeed.com/viewjob?jk=a4e3fcf4a7d4de9e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R&amp;D Senior Consultant</t>
+          <t>Sr Software Engineer, Fullstack (Developer Productivity)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Yokogawa</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Santa Fe, NM, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4267dc9b6e685a7</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Data Analyst, Business Analysis and Reporting - Lakeland</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Publix</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Lakeland, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, NoSQL, Tableau, Power BI, MicroStrategy, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=18433bb8892f8bce</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>LTSS &amp; Dual Eligible Program Report Developer IV</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CareSource</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>10</v>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>RAG, Data Lake, Docker, Kubernetes, CI/CD, Git, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>CI/CD, Databricks, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e6246aba8708cc71</t>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc73004eb58729f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Gemini, Kubernetes, CI/CD, Git, R, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=881bb762adef678a</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Software Architect</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Powder Springs, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2cbc6b59d26185c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior ML Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Exact Sciences</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Python, R</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b109dae448b56c1</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-27.xlsx
+++ b/daily_matches/job_matches_2026-03-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,165 +468,165 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GCP AI Engineer</t>
+          <t>Senior Software Engineer - AI and Automation, Data &amp; Analytics | USA | Remote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Grafana Labs</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.4</v>
+        <v>14.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Gemini, TensorFlow, PyTorch, Data Lake, Docker</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Pinecone, ChromaDB, BigQuery, BigQuery, Python, SQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90a4bbd6dc8ae1d0</t>
+          <t>https://www.indeed.com/viewjob?jk=80830d8b80c7598f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI/ML Engineer with AWS SageMaker</t>
+          <t>Senior Engineer - GenAI Engineering</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>GE Vernova</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.2</v>
+        <v>11.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Gemini, TensorFlow, PyTorch, XGBoost, AWS SageMaker, S3</t>
+          <t>AI Engineer, Generative AI, RAG, Hugging Face, Prompt Engineering, PyTorch, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3717cba2b9262b6d</t>
+          <t>https://www.indeed.com/viewjob?jk=68a0f6931e6dd8c6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>R&amp;D Senior Consultant (Senior Full Stack Developer)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>KBC Global</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Santa Fe, NM, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, TensorFlow, PyTorch, Redshift, Git, Snowflake, Redshift</t>
+          <t>RAG, Data Lake, Docker, Kubernetes, CI/CD, Git, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
+          <t>https://www.indeed.com/viewjob?jk=528c901ad7f48fe6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Infrastructure DevOps Engineer</t>
+          <t>Cloud Analytics Infrastructure Engineer-Remote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Grady Health System</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wellington, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>10</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Gemini, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>AI Engineer, RAG, Docker, Kubernetes, CI/CD, Tableau, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36619f835bea4f18</t>
+          <t>https://www.indeed.com/viewjob?jk=36dd8ba29ee9494b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Java Python Full Stack Developer</t>
+          <t>Engineer, Development Tax Technology | Atlanta Summer/Fall 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL</t>
+          <t>RAG, AKS, Git, Databricks, Tableau, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,497 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1dd947a7f977e8c</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Infrastructure Engineer (Backend)</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>RAG, Glue, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9275dfa105600f9f</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Infrastructure Engineer (Backend)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>RAG, Glue, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fbda2b1be4a20921</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Infrastructure Engineer (Backend)</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>RAG, Glue, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer - APIs</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>HCA Healthcare</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, Dataflow, Kubernetes, CI/CD, Git, BigQuery, Kafka, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=734740ee36ff607d</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Sr Data Scientist</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>AT&amp;T</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Keras, MLflow, Databricks, Python</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=38426988b285acce</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Software Engineer III (Java/SpringBoot/Kafka/Cloud)</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Terraform, Git, Snowflake, Kafka, Cassandra, NoSQL, SQL, R</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e37f813b5cb175d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Associate Data Scientist</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>University of Southern California</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Redshift, Git, Snowflake, Redshift, MySQL, NoSQL, Tableau, Python</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9a2a8cc873c5ddd1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Consultant Analytical Engineer Expanse</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>HCA Healthcare</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, Redshift, Hadoop, Tableau, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a4e3fcf4a7d4de9e</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Sr Software Engineer, Fullstack (Developer Productivity)</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b4267dc9b6e685a7</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Data Analyst, Business Analysis and Reporting - Lakeland</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Publix</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Lakeland, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, NoSQL, Tableau, Power BI, MicroStrategy, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=18433bb8892f8bce</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>LTSS &amp; Dual Eligible Program Report Developer IV</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>CareSource</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>CI/CD, Databricks, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cc73004eb58729f0</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, Gemini, Kubernetes, CI/CD, Git, R, Scala</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=881bb762adef678a</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Software Architect</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Powder Springs, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2cbc6b59d26185c0</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Senior ML Engineer</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Exact Sciences</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Python, R</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2b109dae448b56c1</t>
+          <t>https://www.indeed.com/viewjob?jk=5a1e1b9a56352414</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-27.xlsx
+++ b/daily_matches/job_matches_2026-03-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - AI and Automation, Data &amp; Analytics | USA | Remote</t>
+          <t>Python Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Grafana Labs</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.4</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, Pinecone, ChromaDB, BigQuery, BigQuery, Python, SQL</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, Prompt Engineering, FastAPI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80830d8b80c7598f</t>
+          <t>https://www.indeed.com/viewjob?jk=9213a181d4a91817</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Engineer - GenAI Engineering</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GE Vernova</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.1</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Hugging Face, Prompt Engineering, PyTorch, Git, Python, R, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, TensorFlow, PyTorch, MLflow</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68a0f6931e6dd8c6</t>
+          <t>https://www.indeed.com/viewjob?jk=cb559ab77acb7f90</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R&amp;D Senior Consultant (Senior Full Stack Developer)</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KBC Global</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Santa Fe, NM, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Docker, Kubernetes, CI/CD, Git, R, Java, Optimization</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, S3, Glue, Docker, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=528c901ad7f48fe6</t>
+          <t>https://www.indeed.com/viewjob?jk=fd934ff3fd857de0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cloud Analytics Infrastructure Engineer-Remote</t>
+          <t>AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Grady Health System</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Docker, Kubernetes, CI/CD, Tableau, R, Scala, Optimization</t>
+          <t>Generative AI, LangChain, TensorFlow, PyTorch, S3, EC2, Docker, Kubernetes, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,42 +601,777 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36dd8ba29ee9494b</t>
+          <t>https://www.indeed.com/viewjob?jk=90ae4f8d8427460d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Engineer, Development Tax Technology | Atlanta Summer/Fall 2026</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, MLflow</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=183f049fa74964b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MLOps</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, PySpark, PostgreSQL, MySQL</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c542148e5993d901</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ML Infrastructure Architect</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, FastAPI, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9e27726cfa0e5d0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ML Infrastructure Architect</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, TensorFlow, PyTorch, S3, EC2, Docker, Kubernetes, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3a69de16b0a90c6c</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ML Infrastructure Architect</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, FastAPI, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=95e28857e9f9f7a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TypeScript Architect</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAG, AWS SageMaker, S3, Glue, Athena, Redshift, Data Lake, Terraform, Redshift, Tableau</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=44ba37f68be27f24</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Product Analytics, Senior Associate</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>athenahealth</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Belfast, ME, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, Prompt Engineering, Cortex, Athena, AKS, CI/CD, Git, Snowflake, Tableau</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=13e9aeecafcd087e</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Product Analytics, Associate</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>athenahealth</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Belfast, ME, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, Prompt Engineering, Cortex, Athena, AKS, CI/CD, Git, Snowflake, Tableau</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21f8191c9528fa3a</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>GCP Support Associate</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CT, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, BigQuery, Docker, Kubernetes, CI/CD, BigQuery, NoSQL</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81f94f1493f55928</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AI Data Scientist</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Summit Utilities, Inc.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Fort Smith, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Data Scientist, Azure ML, Synapse, AKS, Git, Snowflake, Databricks, Matplotlib, Seaborn, Python</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2fec50f02a5ef6aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AI Data Scientist</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Summit Utilities, Inc.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Fayetteville, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Data Scientist, Azure ML, Synapse, AKS, Git, Snowflake, Databricks, Matplotlib, Seaborn, Python</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=faa9dfb3a4929603</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AI Data Scientist</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Summit Utilities, Inc.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Little Rock, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Data Scientist, Azure ML, Synapse, AKS, Git, Snowflake, Databricks, Matplotlib, Seaborn, Python</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba51b0aca980bb32</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ML Infrastructure Architect</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, FastAPI, Docker, Kubernetes, CI/CD</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1902c3fe2c603ea3</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Data Developer - L2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Verisk</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Holmdel, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Redshift, BigQuery, Data Lake, CI/CD, Snowflake, Databricks, BigQuery, Redshift, Tableau, Python</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a6f9f9b97c543b71</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>PingOne Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Kafka, Python, R</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=18c12109a7451aa2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PingOne Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, AKS, CI/CD, Terraform, Git, Kafka, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=23deb32319c32c11</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ML Infrastructure Architect</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Hugging Face, TensorFlow, PyTorch, Keras, spaCy, FastAPI, Kubernetes, Python, R</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bb61f40ace52fce3</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>GCP Support Associate</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Dataflow, CI/CD, Terraform, BigQuery, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=89014203bf3a9be6</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Software Engineer III (Full Stack) – API Gateway Platform</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, S3, Glue, Athena, Docker, Kubernetes, Git, R, Java</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=43eddb2055275119</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AI Developer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Recutify Inc.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Dearborn, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, PyTorch, FastAPI, Docker, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0804dace67eceacf</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ML Infrastructure Architect</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, Hugging Face, TensorFlow, PyTorch, Python, R</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1f85a9a149e5351d</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Data Scientist - GenBI</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>The Home Depot</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
           <t>Atlanta, GA, US USA</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D27" t="n">
         <v>10</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>RAG, AKS, Git, Databricks, Tableau, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5a1e1b9a56352414</t>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8ee6a003bc7a491a</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-27.xlsx
+++ b/daily_matches/job_matches_2026-03-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Python Architect</t>
+          <t>Sr. Software Developer Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, Prompt Engineering, FastAPI</t>
+          <t>LangChain, RAG, LLaMA, Prompt Engineering, Docker, Kubernetes, CI/CD, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9213a181d4a91817</t>
+          <t>https://www.indeed.com/viewjob?jk=26bbbe2a65f6b2da</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Senior, Data Scientist</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, TensorFlow, PyTorch, MLflow</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kubernetes, Git, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb559ab77acb7f90</t>
+          <t>https://www.indeed.com/viewjob?jk=1e347cfbf683cf04</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Magna International</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lowell, MA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, S3, Glue, Docker, CI/CD, Jenkins</t>
+          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Tableau, Power BI, Quicksight</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd934ff3fd857de0</t>
+          <t>https://www.indeed.com/viewjob?jk=0ffcdaf2a52019fa</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Issaquah, WA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, TensorFlow, PyTorch, S3, EC2, Docker, Kubernetes, CI/CD, Terraform</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Azure ML, Docker, Kubernetes, CI/CD, Databricks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90ae4f8d8427460d</t>
+          <t>https://www.indeed.com/viewjob?jk=81d0fe049db3a5c5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, MLflow</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Azure ML, Docker, Kubernetes, CI/CD, Databricks</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=183f049fa74964b2</t>
+          <t>https://www.indeed.com/viewjob?jk=4966d5bf8d7c4665</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Issaquah, WA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, PySpark, PostgreSQL, MySQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Azure ML, Docker, Kubernetes, CI/CD, Databricks</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c542148e5993d901</t>
+          <t>https://www.indeed.com/viewjob?jk=da5500cd01d24e3b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, FastAPI, Docker, Kubernetes</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Azure ML, Docker, Kubernetes, CI/CD, Databricks</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e27726cfa0e5d0f</t>
+          <t>https://www.indeed.com/viewjob?jk=116d2aae5d42caac</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Analytics &amp; AI Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Vessco Water</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chanhassen, MN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, TensorFlow, PyTorch, S3, EC2, Docker, Kubernetes, CI/CD, Terraform</t>
+          <t>RAG, Copilot, BigQuery, Synapse, Snowflake, Databricks, BigQuery, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a69de16b0a90c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=9c5a01cb73725f2f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Data Developer - L2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ignite Insurance Systems</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Holmdel, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, FastAPI, Docker, Kubernetes</t>
+          <t>Redshift, BigQuery, Data Lake, CI/CD, Snowflake, Databricks, BigQuery, Redshift, Tableau, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95e28857e9f9f7a2</t>
+          <t>https://www.indeed.com/viewjob?jk=c72f53b3836fad3b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TypeScript Architect</t>
+          <t>AI Developer Associate</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, AWS SageMaker, S3, Glue, Athena, Redshift, Data Lake, Terraform, Redshift, Tableau</t>
+          <t>AI Engineer, RAG, Copilot, Prompt Engineering, CI/CD, Git, Databricks, Power BI, Python, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44ba37f68be27f24</t>
+          <t>https://www.indeed.com/viewjob?jk=59b77f9d516d7bfd</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Product Analytics, Senior Associate</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Belfast, ME, US USA</t>
+          <t>Greenville, DE, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Prompt Engineering, Cortex, Athena, AKS, CI/CD, Git, Snowflake, Tableau</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, LightGBM, Keras, Snowflake, NoSQL, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13e9aeecafcd087e</t>
+          <t>https://www.indeed.com/viewjob?jk=a50bb2dabed0081e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Product Analytics, Associate</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Belfast, ME, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Prompt Engineering, Cortex, Athena, AKS, CI/CD, Git, Snowflake, Tableau</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, LightGBM, Keras, Snowflake, NoSQL, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21f8191c9528fa3a</t>
+          <t>https://www.indeed.com/viewjob?jk=9cb87d9a28b1feb7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>project44</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, BigQuery, Docker, Kubernetes, CI/CD, BigQuery, NoSQL</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, Git, Snowflake, Databricks, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81f94f1493f55928</t>
+          <t>https://www.indeed.com/viewjob?jk=1a8813cf22d6aede</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Cloud Ops Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Summit Utilities, Inc.</t>
+          <t>OneTrust</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Fort Smith, AR, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, Azure ML, Synapse, AKS, Git, Snowflake, Databricks, Matplotlib, Seaborn, Python</t>
+          <t>RAG, Kubernetes, Terraform, Git, Kafka, MongoDB, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,102 +951,102 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fec50f02a5ef6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=c316617b8024464e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Summit Utilities, Inc.</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Fayetteville, AR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, Azure ML, Synapse, AKS, Git, Snowflake, Databricks, Matplotlib, Seaborn, Python</t>
+          <t>RAG, Copilot, CI/CD, Git, Kafka, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faa9dfb3a4929603</t>
+          <t>https://www.indeed.com/viewjob?jk=e4a087bbfc74bb05</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Summit Utilities, Inc.</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, Azure ML, Synapse, AKS, Git, Snowflake, Databricks, Matplotlib, Seaborn, Python</t>
+          <t>RAG, Copilot, CI/CD, Git, Kafka, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba51b0aca980bb32</t>
+          <t>https://www.indeed.com/viewjob?jk=1b283ba99e10e1ba</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Stride, Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, FastAPI, Docker, Kubernetes, CI/CD</t>
+          <t>RAG, Git, Snowflake, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1902c3fe2c603ea3</t>
+          <t>https://www.indeed.com/viewjob?jk=e61979ae0a58dd80</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Developer - L2</t>
+          <t>Data Solution Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Verisk</t>
+          <t>SimilarWeb</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Holmdel, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Data Lake, CI/CD, Snowflake, Databricks, BigQuery, Redshift, Tableau, Python</t>
+          <t>RAG, S3, Git, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6f9f9b97c543b71</t>
+          <t>https://www.indeed.com/viewjob?jk=57dda46ad6b7a646</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>AI and Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Proterial</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Kafka, Python, R</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18c12109a7451aa2</t>
+          <t>https://www.indeed.com/viewjob?jk=399765d41b7cdb68</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Data Scientist – Applied AI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wingstop</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, Terraform, Git, Kafka, SQL, R, Java</t>
+          <t>Data Scientist, Generative AI, Snowflake, Databricks, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23deb32319c32c11</t>
+          <t>https://www.indeed.com/viewjob?jk=0174a84a5c7b5c8c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Senior Data Scientist – Applied AI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wingstop</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Hugging Face, TensorFlow, PyTorch, Keras, spaCy, FastAPI, Kubernetes, Python, R</t>
+          <t>Data Scientist, Generative AI, Snowflake, Databricks, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,182 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb61f40ace52fce3</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>GCP Support Associate</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>IL, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, Dataflow, CI/CD, Terraform, BigQuery, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=89014203bf3a9be6</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Software Engineer III (Full Stack) – API Gateway Platform</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>RAG, S3, Glue, Athena, Docker, Kubernetes, Git, R, Java</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=43eddb2055275119</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>AI Developer</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Recutify Inc.</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Dearborn, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, PyTorch, FastAPI, Docker, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0804dace67eceacf</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>ML Infrastructure Architect</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, Hugging Face, TensorFlow, PyTorch, Python, R</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1f85a9a149e5351d</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Data Scientist - GenBI</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>The Home Depot</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8ee6a003bc7a491a</t>
+          <t>https://www.indeed.com/viewjob?jk=e19bbac2aebb38ef</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-27.xlsx
+++ b/daily_matches/job_matches_2026-03-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr. Software Developer Engineer</t>
+          <t>REFRAME Platform Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>North Carolina State University</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Prompt Engineering, Docker, Kubernetes, CI/CD, PostgreSQL, MySQL, MongoDB</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, AWS SageMaker, GCP Vertex AI, Azure ML, MLflow, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26bbbe2a65f6b2da</t>
+          <t>https://www.indeed.com/viewjob?jk=f51272f2fb3899cf</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior, Data Scientist</t>
+          <t>Gen AI Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kubernetes, Git, Databricks, Python, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e347cfbf683cf04</t>
+          <t>https://www.indeed.com/viewjob?jk=4b06a736d2a9a21f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Data Engineer (GCP, Snowflake)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Magna International</t>
+          <t>Addepto</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Lowell, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Tableau, Power BI, Quicksight</t>
+          <t>Data Scientist, RAG, BigQuery, CI/CD, Terraform, Git, Snowflake, Databricks, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ffcdaf2a52019fa</t>
+          <t>https://www.indeed.com/viewjob?jk=171e4e9a5f95f349</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>AFD360 Solution Engineer - Regulated Industries</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Informatica</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Issaquah, WA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Azure ML, Docker, Kubernetes, CI/CD, Databricks</t>
+          <t>RAG, Gemini, BigQuery, Snowflake, Databricks, BigQuery, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81d0fe049db3a5c5</t>
+          <t>https://www.indeed.com/viewjob?jk=8f08bed697dbfd0d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Technical Support Engineer - Agentforce / Data360 - Spanish or Portuguese Speaking</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Informatica</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Azure ML, Docker, Kubernetes, CI/CD, Databricks</t>
+          <t>Generative AI, RAG, Prompt Engineering, Redshift, Git, Snowflake, Redshift, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4966d5bf8d7c4665</t>
+          <t>https://www.indeed.com/viewjob?jk=fc9f1867a3f8de54</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Issaquah, WA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Azure ML, Docker, Kubernetes, CI/CD, Databricks</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da5500cd01d24e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=228735d95aa39905</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Azure ML, Docker, Kubernetes, CI/CD, Databricks</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116d2aae5d42caac</t>
+          <t>https://www.indeed.com/viewjob?jk=71d644559bdc6921</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Analytics &amp; AI Architect</t>
+          <t>Data Architect (GCP, Snowflake)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Vessco Water</t>
+          <t>Addepto</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chanhassen, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, BigQuery, Synapse, Snowflake, Databricks, BigQuery, Tableau, Power BI, Python</t>
+          <t>Data Scientist, RAG, BigQuery, Terraform, Snowflake, Databricks, BigQuery, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c5a01cb73725f2f</t>
+          <t>https://www.indeed.com/viewjob?jk=13a9ab76e83e7683</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Developer - L2</t>
+          <t>Performance Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ignite Insurance Systems</t>
+          <t>Informatica</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Holmdel, NJ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Data Lake, CI/CD, Snowflake, Databricks, BigQuery, Redshift, Tableau, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c72f53b3836fad3b</t>
+          <t>https://www.indeed.com/viewjob?jk=f2299267620bf729</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Developer Associate</t>
+          <t>Software Engineer, Search Data Infrastructure -Slack</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Informatica</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Prompt Engineering, CI/CD, Git, Databricks, Power BI, Python, R</t>
+          <t>Machine Learning Engineer, Generative AI, Kubernetes, Terraform, Hadoop, MySQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59b77f9d516d7bfd</t>
+          <t>https://www.indeed.com/viewjob?jk=e37ebd15ca180f03</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>LINDY</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Greenville, DE, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, LightGBM, Keras, Snowflake, NoSQL, Python</t>
+          <t>RAG, BigQuery, Snowflake, BigQuery, Tableau, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a50bb2dabed0081e</t>
+          <t>https://www.indeed.com/viewjob?jk=6fc0173daf7dd298</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Backend Software Engineer (contract)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, LightGBM, Keras, Snowflake, NoSQL, Python</t>
+          <t>RAG, Prompt Engineering, CI/CD, Kafka, MongoDB, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cb87d9a28b1feb7</t>
+          <t>https://www.indeed.com/viewjob?jk=315d1dcf2897cbfc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Sr Data Analyst</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>project44</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Git, Snowflake, Databricks, Kafka, Python, SQL, R</t>
+          <t>Data Scientist, BigQuery, Snowflake, BigQuery, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a8813cf22d6aede</t>
+          <t>https://www.indeed.com/viewjob?jk=5e1200f72ec28f1a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cloud Ops Engineer</t>
+          <t>Sr Data Analyst</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>OneTrust</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, Terraform, Git, Kafka, MongoDB, Python, SQL, R, Scala</t>
+          <t>Data Scientist, BigQuery, Snowflake, BigQuery, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c316617b8024464e</t>
+          <t>https://www.indeed.com/viewjob?jk=3ed05d5559970a49</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Security Engineer (Distributed Systems)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Informatica</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, Kafka, NoSQL, SQL, R, Java, Scala</t>
+          <t>RAG, Gemini, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4a087bbfc74bb05</t>
+          <t>https://www.indeed.com/viewjob?jk=f5e9c5b32ee53540</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DevOps Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>CyberArk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, Kafka, NoSQL, SQL, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b283ba99e10e1ba</t>
+          <t>https://www.indeed.com/viewjob?jk=374cb42647c9f2d9</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Data Engineer - Oklahoma City, OK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Stride, Inc.</t>
+          <t>CFS Brands, LLC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Git, Snowflake, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Cortex, Snowflake, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e61979ae0a58dd80</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb492a67fde6480</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Solution Engineer</t>
+          <t>Agentic Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SimilarWeb</t>
+          <t>Rotolo Consultants, Inc. (RCI)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Slidell, LA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, S3, Git, Snowflake, Databricks, Python, SQL, R, Scala</t>
+          <t>RAG, Prompt Engineering, Cortex, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57dda46ad6b7a646</t>
+          <t>https://www.indeed.com/viewjob?jk=ca804bf336f080bf</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI and Data Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Proterial</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, Git, Python, R, Scala</t>
+          <t>Data Scientist, RAG, Data Lake, Kinesis, Git, Databricks, PySpark, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=399765d41b7cdb68</t>
+          <t>https://www.indeed.com/viewjob?jk=f77a2037f942c65a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Applied AI</t>
+          <t>Senior Software Engineer | Cloud</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Wingstop</t>
+          <t>ExtraHop Networks</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, Snowflake, Databricks, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, S3, EC2, Kubernetes, CI/CD, Terraform, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,42 +1161,427 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0174a84a5c7b5c8c</t>
+          <t>https://www.indeed.com/viewjob?jk=37a7ab8a80b65ab4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Applied AI</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Wingstop</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=82581067608cfb2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>WEX Inc.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, LightGBM, AWS SageMaker, Docker, CI/CD, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c4af220af6ec736f</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Informatica</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Mexico, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
         <v>10</v>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, Snowflake, Databricks, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e19bbac2aebb38ef</t>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, CI/CD, Git, Snowflake, Kafka, R, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eabefa51e4976b97</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>DevOps Engineer, Data Ingestion</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ProRATA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, MongoDB, SQL, R</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=75a383a5d33ab180</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Associate Engineer, Product Software</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Equinix</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Redwood City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>S3, Docker, GitHub Actions, Git, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=648c7e65d7d214bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Associate Software Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Equinix</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AI Engineer, Prompt Engineering, Kubernetes, CI/CD, Git, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f744665d3dc89e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Data Science Associate</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Hyundai Capital America</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, Prompt Engineering, CI/CD, SQL, R, Scala, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=63336f9931f64014</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Sr. Platform Software Engineer – AI and Innovation</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Inspira Financial</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Oak Brook, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Git, PostgreSQL, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=caa447cd9431af9a</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SDET (Software Development Engineering in Test)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Involgix</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, R, Java</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a94344241798565</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Asset &amp; Wealth Management-Front-End Developer -Associate-Dallas</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=11cbeaa457ae6a94</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior Analyst, Search and Recommendations</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CarMax</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Data Scientist, Git, Databricks, Tableau, Matplotlib, Python, SQL, R, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=264ac1343853185d</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Engineer/Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=56349462fbeb65b4</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-27.xlsx
+++ b/daily_matches/job_matches_2026-03-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>REFRAME Platform Architect</t>
+          <t>GCP ML Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>North Carolina State University</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, AWS SageMaker, GCP Vertex AI, Azure ML, MLflow, Docker</t>
+          <t>Generative AI, RAG, LLaMA, Copilot, Hugging Face, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f51272f2fb3899cf</t>
+          <t>https://www.indeed.com/viewjob?jk=0898e60057ca64e0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Gen AI Developer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, S3, Glue, Athena, Redshift, Data Lake, MLflow</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b06a736d2a9a21f</t>
+          <t>https://www.indeed.com/viewjob?jk=cab1a7566b504833</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer (GCP, Snowflake)</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Addepto</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, CI/CD, Terraform, Git, Snowflake, Databricks, BigQuery, Tableau</t>
+          <t>AI Engineer, Generative AI, LangChain, TensorFlow, PyTorch, S3, EC2, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=171e4e9a5f95f349</t>
+          <t>https://www.indeed.com/viewjob?jk=1a8e3179e23b63c6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AFD360 Solution Engineer - Regulated Industries</t>
+          <t>Associate, AI/ML Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Informatica</t>
+          <t>Legend Biotech</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Somerset, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Gemini, BigQuery, Snowflake, Databricks, BigQuery, Tableau, Power BI, Python, SQL</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, MLflow, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f08bed697dbfd0d</t>
+          <t>https://www.indeed.com/viewjob?jk=25105df2cbf32f18</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Technical Support Engineer - Agentforce / Data360 - Spanish or Portuguese Speaking</t>
+          <t>Gen AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Informatica</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, Redshift, Git, Snowflake, Redshift, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9f1867a3f8de54</t>
+          <t>https://www.indeed.com/viewjob?jk=490af5a2f7c466cb</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Python AI Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, Python, R</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=228735d95aa39905</t>
+          <t>https://www.indeed.com/viewjob?jk=8f2b8b969b492461</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Science Intern - Summer 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Xome Realty Services</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, Python, R</t>
+          <t>Data Scientist, RAG, Copilot, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d644559bdc6921</t>
+          <t>https://www.indeed.com/viewjob?jk=054c13e073e154f5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Architect (GCP, Snowflake)</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Addepto</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Terraform, Snowflake, Databricks, BigQuery, Python, SQL, R</t>
+          <t>AI Engineer, Machine Learning Engineer, RAG, LLaMA, Gemini, Mistral, FAISS, Pinecone, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13a9ab76e83e7683</t>
+          <t>https://www.indeed.com/viewjob?jk=70365856f4031b9e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Performance Engineer</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Informatica</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2299267620bf729</t>
+          <t>https://www.indeed.com/viewjob?jk=1541a87a2c01b500</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer, Search Data Infrastructure -Slack</t>
+          <t>Senior AI Developer/Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Informatica</t>
+          <t>Colorado Health Benefit Exchange</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, Kubernetes, Terraform, Hadoop, MySQL, Python, SQL, R, Java</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Cortex, FastAPI, CI/CD, Snowflake, PostgreSQL, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e37ebd15ca180f03</t>
+          <t>https://www.indeed.com/viewjob?jk=c4efcfdcf2b8a5e3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Developer/Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LINDY</t>
+          <t>Colorado Health Benefit Exchange</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Snowflake, BigQuery, Tableau, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, Cortex, S3, FastAPI, CI/CD, Git, Snowflake, PostgreSQL, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fc0173daf7dd298</t>
+          <t>https://www.indeed.com/viewjob?jk=0521ea19aa9bca8e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (contract)</t>
+          <t>CrowdStrike Cloud Security Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, CI/CD, Kafka, MongoDB, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=315d1dcf2897cbfc</t>
+          <t>https://www.indeed.com/viewjob?jk=4f7d575b2b9d3334</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr Data Analyst</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, BigQuery, Snowflake, BigQuery, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e1200f72ec28f1a</t>
+          <t>https://www.indeed.com/viewjob?jk=1b78d4a2efec5181</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr Data Analyst</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, BigQuery, Snowflake, BigQuery, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ed05d5559970a49</t>
+          <t>https://www.indeed.com/viewjob?jk=9842bdf5e0800504</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Security Engineer (Distributed Systems)</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Informatica</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5e9c5b32ee53540</t>
+          <t>https://www.indeed.com/viewjob?jk=a27a3bbd4f75b8e2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DevOps Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CyberArk</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+          <t>Generative AI, RAG, Gemini, BigQuery, Docker, Kubernetes, CI/CD, Terraform, Git, BigQuery</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=374cb42647c9f2d9</t>
+          <t>https://www.indeed.com/viewjob?jk=65b9e64510577fb6</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer - Oklahoma City, OK</t>
+          <t>Google Cloud Solution Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CFS Brands, LLC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Cortex, Snowflake, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, Gemini, BigQuery, Docker, Kubernetes, CI/CD, Terraform, Git, BigQuery</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb492a67fde6480</t>
+          <t>https://www.indeed.com/viewjob?jk=34b99631b1e6f2b1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Agentic Engineer</t>
+          <t>Mid-Level Data Scientist</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Rotolo Consultants, Inc. (RCI)</t>
+          <t>USAA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Slidell, LA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Cortex, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R, Java</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Git, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca804bf336f080bf</t>
+          <t>https://www.indeed.com/viewjob?jk=d278b9c7e349efba</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Kinesis, Git, Databricks, PySpark, SQL, R, Scala</t>
+          <t>AI Engineer, Data Scientist, TensorFlow, PyTorch, Docker, Kubernetes, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77a2037f942c65a</t>
+          <t>https://www.indeed.com/viewjob?jk=a4bafde71ede2406</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer | Cloud</t>
+          <t>Sr Machine Learning Engineer New</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ExtraHop Networks</t>
+          <t>Convey</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Kubernetes, CI/CD, Terraform, Python, R, Scala, Optimization</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, Git, Snowflake, Databricks, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37a7ab8a80b65ab4</t>
+          <t>https://www.indeed.com/viewjob?jk=543473e52b80856a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Applied AI Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Cordial</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Prompt Engineering, NoSQL, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82581067608cfb2b</t>
+          <t>https://www.indeed.com/viewjob?jk=b680b6532cfa4719</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, LightGBM, AWS SageMaker, Docker, CI/CD, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Python, R, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4af220af6ec736f</t>
+          <t>https://www.indeed.com/viewjob?jk=6997a954890f2aa5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GCP ML Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Informatica</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Mexico, MO, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, CI/CD, Git, Snowflake, Kafka, R, Scala</t>
+          <t>Data Scientist, TensorFlow, PyTorch, Docker, Kubernetes, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eabefa51e4976b97</t>
+          <t>https://www.indeed.com/viewjob?jk=ce109653891dcb6c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Data Ingestion</t>
+          <t>Sr Firmware DevOps Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ProRATA</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, MongoDB, SQL, R</t>
+          <t>Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75a383a5d33ab180</t>
+          <t>https://www.indeed.com/viewjob?jk=6171331838e8d021</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Associate Engineer, Product Software</t>
+          <t>Senior Analyst Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Equinix</t>
+          <t>Howmet Aerospace</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Whitehall, MI, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>S3, Docker, GitHub Actions, Git, NoSQL, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Data Lake, Git, Databricks, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648c7e65d7d214bc</t>
+          <t>https://www.indeed.com/viewjob?jk=ae39c61c9537eb89</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Equinix</t>
+          <t>Edwards Lifesciences</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AI Engineer, Prompt Engineering, Kubernetes, CI/CD, Git, Kafka, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Git, Snowflake, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f744665d3dc89e3</t>
+          <t>https://www.indeed.com/viewjob?jk=f659f9a6250b623d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Science Associate</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Hyundai Capital America</t>
+          <t>Pinwheel</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, Prompt Engineering, CI/CD, SQL, R, Scala, Optimization, A/B Testing</t>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63336f9931f64014</t>
+          <t>https://www.indeed.com/viewjob?jk=39623d8a5533afdf</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Platform Software Engineer – AI and Innovation</t>
+          <t>CrowdStrike Automation Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Inspira Financial</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Git, PostgreSQL, SQL, R, Scala, Optimization</t>
+          <t>Prompt Engineering, CI/CD, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caa447cd9431af9a</t>
+          <t>https://www.indeed.com/viewjob?jk=96a86567f4793da1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SDET (Software Development Engineering in Test)</t>
+          <t>GCP ML Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Involgix</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, R, Java</t>
+          <t>AI Engineer, Machine Learning Engineer, RAG, TensorFlow, PyTorch, CI/CD, Python, R, Bayesian</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a94344241798565</t>
+          <t>https://www.indeed.com/viewjob?jk=2ced137c72152382</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management-Front-End Developer -Associate-Dallas</t>
+          <t>Global Tapeout and Mask Operations, Biz App and Data Engineer (2026 New College Graduate)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>GlobalFoundries</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>Jenkins, Git, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11cbeaa457ae6a94</t>
+          <t>https://www.indeed.com/viewjob?jk=b8ebfb0268153921</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Analyst, Search and Recommendations</t>
+          <t>IT Intern</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Peabody Energy</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Data Scientist, Git, Databricks, Tableau, Matplotlib, Python, SQL, R, Hypothesis Testing</t>
+          <t>Generative AI, TensorFlow, PyTorch, Tableau, Power BI, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,42 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=264ac1343853185d</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=56349462fbeb65b4</t>
+          <t>https://www.indeed.com/viewjob?jk=e8246f9db8dacd64</t>
         </is>
       </c>
     </row>
